--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486862_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486862_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5719</v>
+        <v>7.1535</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8745</v>
+        <v>5.4561</v>
       </c>
       <c r="F2" t="n">
         <v>1.6974</v>
@@ -610,10 +610,10 @@
         <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0267</v>
+        <v>0.6083</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8677</v>
+        <v>0.4493</v>
       </c>
       <c r="U2" t="n">
         <v>0.159</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. FRITZ</t>
+          <t>I. CORRALIZA COBA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8569</v>
+        <v>1.7492</v>
       </c>
       <c r="E3" t="n">
-        <v>1.874</v>
+        <v>1.1673</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0171</v>
+        <v>0.5819</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.5936</v>
+        <v>2.845</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.6963</v>
+        <v>-0.723</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1027</v>
+        <v>3.568</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4524</v>
+        <v>4.1042</v>
       </c>
       <c r="K3" t="n">
-        <v>0.166</v>
+        <v>1.0259</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6183999999999999</v>
+        <v>3.0783</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1412</v>
+        <v>-1.2592</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8623</v>
+        <v>-1.7489</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7211</v>
+        <v>0.4897</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.0267</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0267</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7011</v>
+        <v>1.0665</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4333</v>
+        <v>0.1432</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2678</v>
+        <v>0.9232</v>
       </c>
       <c r="V3" t="n">
-        <v>2.7762</v>
+        <v>-0.5195</v>
       </c>
       <c r="W3" t="n">
-        <v>2.9466</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1704</v>
+        <v>-0.5195</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7609</v>
+        <v>1.583</v>
       </c>
       <c r="E4" t="n">
         <v>1.7317</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0292</v>
+        <v>-0.1487</v>
       </c>
       <c r="G4" t="n">
         <v>0.8084</v>
@@ -766,13 +766,13 @@
         <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0023</v>
+        <v>-0.1801</v>
       </c>
       <c r="T4" t="n">
         <v>0.1122</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1145</v>
+        <v>-0.2924</v>
       </c>
       <c r="V4" t="n">
         <v>2.5975</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. CORRALIZA COBA</t>
+          <t>O. BIESHAAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4898</v>
+        <v>0.7776</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9968</v>
+        <v>1.1065</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4929</v>
+        <v>-0.3288</v>
       </c>
       <c r="G5" t="n">
-        <v>2.845</v>
+        <v>1.3577</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.723</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>3.568</v>
+        <v>1.9419</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1042</v>
+        <v>1.7226</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0259</v>
+        <v>0.5256</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0783</v>
+        <v>1.197</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2592</v>
+        <v>-0.3649</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7489</v>
+        <v>-1.1098</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4897</v>
+        <v>0.7449</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6427</v>
+        <v>0.4107</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
         <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8071</v>
+        <v>0.6684</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0272</v>
+        <v>0.4106</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8343</v>
+        <v>0.2578</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5195</v>
+        <v>-1.6591</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5195</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. BIESHAAR</t>
+          <t>J. FRITZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3599</v>
+        <v>0.6972</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6295</v>
+        <v>0.6847</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2695</v>
+        <v>0.0125</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3577</v>
+        <v>-1.5936</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-1.6963</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9419</v>
+        <v>0.1027</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7226</v>
+        <v>-0.4524</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5256</v>
+        <v>0.166</v>
       </c>
       <c r="L6" t="n">
-        <v>1.197</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3649</v>
+        <v>-1.1412</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1098</v>
+        <v>-1.8623</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7449</v>
+        <v>0.7211</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4107</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2507</v>
+        <v>0.5414</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9336</v>
+        <v>0.244</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3171</v>
+        <v>0.2974</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.6591</v>
+        <v>2.7762</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.9466</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6591</v>
+        <v>-0.1704</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. WELLS</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2924</v>
+        <v>-0.1376</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1429</v>
+        <v>0.1475</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4354</v>
+        <v>-0.2852</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1495</v>
+        <v>-0.2888</v>
       </c>
       <c r="H7" t="n">
-        <v>0.289</v>
+        <v>-0.8758</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1395</v>
+        <v>0.587</v>
       </c>
       <c r="J7" t="n">
-        <v>2.169</v>
+        <v>1.2364</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2877</v>
+        <v>-0.1844</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1188</v>
+        <v>1.4208</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0195</v>
+        <v>-1.5251</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.9988</v>
+        <v>-0.6913</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0207</v>
+        <v>-0.8338</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3096</v>
+        <v>0.2209</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1513</v>
+        <v>-0.0621</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4609</v>
+        <v>0.283</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0698</v>
+        <v>-0.4805</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1088</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>J. WELLS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6607</v>
+        <v>-0.2562</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3755</v>
+        <v>1.2088</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2852</v>
+        <v>-1.465</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2888</v>
+        <v>0.1495</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8758</v>
+        <v>0.289</v>
       </c>
       <c r="I8" t="n">
-        <v>0.587</v>
+        <v>-0.1395</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2364</v>
+        <v>2.169</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1844</v>
+        <v>2.2877</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4208</v>
+        <v>-0.1188</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5251</v>
+        <v>-2.0195</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6913</v>
+        <v>-1.9988</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8338</v>
+        <v>-0.0207</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4107</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3021</v>
+        <v>0.3458</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5851</v>
+        <v>-0.0854</v>
       </c>
       <c r="U8" t="n">
-        <v>0.283</v>
+        <v>0.4312</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4805</v>
+        <v>0.0698</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4805</v>
+        <v>-1.1088</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.2793</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5412</v>
+        <v>0.0864</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2768</v>
+        <v>-0.3658</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2551</v>
@@ -1156,13 +1156,13 @@
         <v>1.4374</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0825</v>
+        <v>0.4562</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2558</v>
+        <v>0.3719</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1733</v>
+        <v>0.0844</v>
       </c>
       <c r="V9" t="n">
         <v>0.1088</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5774</v>
+        <v>-0.6797</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9727</v>
+        <v>-2.4574</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3954</v>
+        <v>1.7776</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3152</v>
+        <v>-2.0783</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6056</v>
+        <v>-1.0285</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9208</v>
+        <v>-1.0499</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0955</v>
+        <v>-1.1556</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4774</v>
+        <v>0.0813</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6181</v>
+        <v>-1.2368</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7803</v>
+        <v>-0.9228</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.083</v>
+        <v>-1.1098</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3027</v>
+        <v>0.187</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8481</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2321</v>
+        <v>1.8481</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5722</v>
+        <v>0.3555</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9881</v>
+        <v>0.2711</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4159</v>
+        <v>0.0844</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5276999999999999</v>
+        <v>1.2484</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7446</v>
+        <v>-0.8995</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2555</v>
+        <v>-2.3838</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5109</v>
+        <v>1.4843</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0783</v>
+        <v>0.3152</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0285</v>
+        <v>-1.6056</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0499</v>
+        <v>1.9208</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1556</v>
+        <v>1.0955</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0813</v>
+        <v>0.4774</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2368</v>
+        <v>0.6181</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9228</v>
+        <v>-0.7803</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1098</v>
+        <v>-2.083</v>
       </c>
       <c r="O11" t="n">
-        <v>0.187</v>
+        <v>1.3027</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2053</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7094</v>
+        <v>0.1056</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.527</v>
+        <v>-0.3992</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1824</v>
+        <v>0.5048</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2484</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.768</v>
+        <v>0.5276999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8005</v>
+        <v>-2.2329</v>
       </c>
       <c r="E12" t="n">
-        <v>0.237</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0375</v>
+        <v>-2.1561</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2247</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6029</v>
+        <v>0.1705</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3098</v>
+        <v>-0.004</v>
       </c>
       <c r="U12" t="n">
-        <v>0.293</v>
+        <v>0.1744</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1786</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.145800000000003</v>
+        <v>7.4753</v>
       </c>
       <c r="E13" t="n">
-        <v>6.341500000000002</v>
+        <v>6.671</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8042999999999996</v>
+        <v>0.8041000000000005</v>
       </c>
       <c r="G13" t="n">
         <v>1.7242</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.7093</v>
+        <v>-5.709299999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>7.433400000000001</v>
+        <v>7.4334</v>
       </c>
       <c r="J13" t="n">
         <v>14.4888</v>
@@ -1456,7 +1456,7 @@
         <v>-13.5961</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8313999999999999</v>
+        <v>0.8314000000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-4.1067</v>
@@ -1468,22 +1468,22 @@
         <v>14.3741</v>
       </c>
       <c r="S13" t="n">
-        <v>4.0296</v>
+        <v>4.359</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1221</v>
+        <v>1.4516</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9074</v>
+        <v>2.9072</v>
       </c>
       <c r="V13" t="n">
-        <v>5.498900000000001</v>
+        <v>5.4989</v>
       </c>
       <c r="W13" t="n">
-        <v>9.211399999999999</v>
+        <v>9.211400000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.712400000000001</v>
+        <v>-3.7124</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6813</v>
+        <v>5.2548</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4849</v>
+        <v>4.0079</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1964</v>
+        <v>1.247</v>
       </c>
       <c r="G14" t="n">
         <v>3.1384</v>
@@ -1546,13 +1546,13 @@
         <v>2.6694</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2991</v>
+        <v>-0.7255</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.178</v>
+        <v>-0.655</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1211</v>
+        <v>-0.0706</v>
       </c>
       <c r="V14" t="n">
         <v>2.2259</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1685</v>
+        <v>3.2024</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0072</v>
+        <v>2.6348</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1613</v>
+        <v>0.5676</v>
       </c>
       <c r="G15" t="n">
         <v>2.2274</v>
@@ -1624,13 +1624,13 @@
         <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.523</v>
+        <v>-0.4892</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7246</v>
+        <v>-0.097</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7984</v>
+        <v>-0.3922</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5893</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9598</v>
+        <v>1.8744</v>
       </c>
       <c r="E16" t="n">
-        <v>2.602</v>
+        <v>2.2882</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6422</v>
+        <v>-0.4138</v>
       </c>
       <c r="G16" t="n">
         <v>0.1291</v>
@@ -1702,13 +1702,13 @@
         <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0011</v>
+        <v>-0.0843</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1704</v>
+        <v>-0.1434</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1692</v>
+        <v>0.0592</v>
       </c>
       <c r="V16" t="n">
         <v>1.4189</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9539</v>
+        <v>1.1362</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4495</v>
+        <v>2.1357</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4956</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>2.4696</v>
@@ -1780,13 +1780,13 @@
         <v>3.2855</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6753</v>
+        <v>-0.1424</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08500000000000001</v>
+        <v>-0.2288</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5903</v>
+        <v>0.0864</v>
       </c>
       <c r="V17" t="n">
         <v>-1.3963</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3383</v>
+        <v>0.2422</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8943</v>
+        <v>-0.5805</v>
       </c>
       <c r="F18" t="n">
-        <v>0.556</v>
+        <v>0.8227</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1868</v>
@@ -1858,13 +1858,13 @@
         <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9729</v>
+        <v>-0.3923</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6587</v>
+        <v>-0.3449</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3142</v>
+        <v>-0.0474</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5471</v>
+        <v>-2.3239</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6267</v>
+        <v>-1.5221</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9203</v>
+        <v>-0.8018</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6338</v>
@@ -1936,13 +1936,13 @@
         <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5293</v>
+        <v>-0.3061</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3294</v>
+        <v>-0.2248</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1999</v>
+        <v>-0.0813</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5893</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6853</v>
+        <v>-3.3436</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1408</v>
+        <v>-2.0362</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5445</v>
+        <v>-1.3074</v>
       </c>
       <c r="G20" t="n">
         <v>-3.6914</v>
@@ -2014,13 +2014,13 @@
         <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9036</v>
+        <v>-0.5618</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4147</v>
+        <v>-0.3101</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4888</v>
+        <v>-0.2517</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9384</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7402</v>
+        <v>-3.4322</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9296</v>
+        <v>-1.6361</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8106</v>
+        <v>-1.7961</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7994</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1449</v>
+        <v>1.6317</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.9443</v>
+        <v>-1.105</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.406</v>
+        <v>2.1652</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7519</v>
+        <v>1.5996</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.158</v>
+        <v>0.5656</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3934</v>
+        <v>-1.6385</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6071</v>
+        <v>0.0321</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7863</v>
+        <v>-1.6706</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6427</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1174</v>
+        <v>-0.3777</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4147</v>
+        <v>-0.3721</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2973</v>
+        <v>-0.0057</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.4661</v>
+        <v>-1.5277</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.1088</v>
+        <v>-0.3491</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3573</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. PAZ VAZQUEZ</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7861</v>
+        <v>-4.0383</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7018</v>
+        <v>-1.1388</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0843</v>
+        <v>-2.8995</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9038</v>
+        <v>-2.7994</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1331</v>
+        <v>1.1449</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0369</v>
+        <v>-3.9443</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5417</v>
+        <v>-0.406</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4896</v>
+        <v>1.7519</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9479</v>
+        <v>-2.158</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4456</v>
+        <v>-2.3934</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3566</v>
+        <v>-0.6071</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.089</v>
+        <v>-1.7863</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6427</v>
+        <v>1.6427</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.1336</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.4908</v>
+        <v>1.6427</v>
       </c>
       <c r="S22" t="n">
-        <v>1.397</v>
+        <v>-0.4156</v>
       </c>
       <c r="T22" t="n">
-        <v>1.348</v>
+        <v>-0.6239</v>
       </c>
       <c r="U22" t="n">
-        <v>0.049</v>
+        <v>0.2084</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6366</v>
+        <v>-2.4661</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.4579</v>
+        <v>-0.1088</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1786</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>S. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8122</v>
+        <v>-5.0205</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0545</v>
+        <v>-4.957</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7577</v>
+        <v>-0.0634</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5266999999999999</v>
+        <v>-1.9038</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6317</v>
+        <v>0.1331</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.105</v>
+        <v>-2.0369</v>
       </c>
       <c r="J23" t="n">
-        <v>2.1652</v>
+        <v>0.5417</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5996</v>
+        <v>1.4896</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5656</v>
+        <v>-0.9479</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6385</v>
+        <v>-2.4456</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0321</v>
+        <v>-1.3566</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6706</v>
+        <v>-1.089</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0534</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.0801</v>
+        <v>-5.1336</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0267</v>
+        <v>3.4908</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7578</v>
+        <v>0.1626</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7905</v>
+        <v>0.0927</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0327</v>
+        <v>0.0699</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.5277</v>
+        <v>-1.6366</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3491</v>
+        <v>-0.4579</v>
       </c>
       <c r="X23" t="n">
         <v>-1.1786</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.1457</v>
+        <v>-6.448499999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8040999999999987</v>
+        <v>-0.8041</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.3415</v>
+        <v>-5.6442</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.724000000000001</v>
+        <v>-1.723999999999999</v>
       </c>
       <c r="H24" t="n">
         <v>5.7094</v>
       </c>
       <c r="I24" t="n">
-        <v>-7.433299999999999</v>
+        <v>-7.4333</v>
       </c>
       <c r="J24" t="n">
         <v>12.7647</v>
@@ -2305,13 +2305,13 @@
         <v>13.596</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.8313000000000007</v>
+        <v>-0.8312999999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-14.4888</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.886800000000001</v>
+        <v>-7.8868</v>
       </c>
       <c r="O24" t="n">
         <v>-6.602</v>
@@ -2326,22 +2326,22 @@
         <v>18.4807</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.0297</v>
+        <v>-3.3323</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.9072</v>
+        <v>-2.9073</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1223</v>
+        <v>-0.4249999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-5.4989</v>
+        <v>-5.498900000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>3.712400000000001</v>
+        <v>3.7124</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.211299999999998</v>
+        <v>-9.2113</v>
       </c>
     </row>
   </sheetData>
